--- a/ACCY122/Tutorial/T01/T1.xlsx
+++ b/ACCY122/Tutorial/T01/T1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2025 UOW\Learning Material\2025 Tutorials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Tutorial/T01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9912241A-2E87-46F2-B21A-8F0733E07962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA3E82-95DC-F54B-952D-04300AF61269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{5791E237-50C4-4F3C-9FBA-44DBC18D103A}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="33600" windowHeight="18760" activeTab="4" xr2:uid="{5791E237-50C4-4F3C-9FBA-44DBC18D103A}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="10" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="65">
   <si>
     <t>ASSETS</t>
   </si>
@@ -237,13 +237,16 @@
   </si>
   <si>
     <t>Capital Intro</t>
+  </si>
+  <si>
+    <t>Net Profit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,8 +261,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,6 +312,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -315,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -330,11 +364,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -382,8 +420,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1027604" y="639634"/>
-          <a:ext cx="5398739" cy="5708121"/>
+          <a:off x="1089208" y="653851"/>
+          <a:ext cx="5953179" cy="5855023"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -944,14 +982,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>33293</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>490770</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>147120</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>147121</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1454,7 +1492,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5266C6B8-DEA9-4608-AC99-9CB36941A1AB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1464,20 +1502,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{143A62ED-56A0-4957-8F15-257DC59AE21C}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.90625" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="13" max="13" width="14.26953125" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.5" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1488,7 +1526,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -1520,7 +1558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F4" t="s">
         <v>38</v>
       </c>
@@ -1537,7 +1575,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1566,7 +1604,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1583,7 +1621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1597,7 +1635,7 @@
         <v>6875</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1614,7 +1652,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4</v>
       </c>
@@ -1631,7 +1669,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5</v>
       </c>
@@ -1648,7 +1686,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1699,7 +1737,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B12" s="8">
         <f>SUM(B11:F11)</f>
         <v>159250</v>
@@ -1733,12 +1771,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F0F937E-4C12-4841-9156-FD60BA99C2BF}">
   <dimension ref="B3:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
         <v>62</v>
       </c>
@@ -1749,7 +1787,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C4" t="s">
         <v>55</v>
       </c>
@@ -1761,7 +1799,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>56</v>
       </c>
@@ -1771,7 +1809,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -1782,7 +1820,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>57</v>
       </c>
@@ -1796,7 +1834,7 @@
         <v>-15000</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>58</v>
       </c>
@@ -1820,200 +1858,307 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F189E0A-D987-4D06-A4FC-507AD72941BD}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5" style="10" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="10"/>
-    <col min="3" max="3" width="10.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="10"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B4" s="10" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
+      <c r="B5" s="13">
+        <v>15000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="12">
+        <v>15000</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="11"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
+      <c r="B6" s="13">
+        <v>-2000</v>
+      </c>
+      <c r="D6">
+        <v>2000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>3</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="B7" s="13">
+        <v>2000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="11">
+        <v>2000</v>
+      </c>
+      <c r="J7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>4</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="B8" s="13">
+        <v>-1500</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="11">
+        <v>-1500</v>
+      </c>
+      <c r="J8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9">
+        <v>800</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>800</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>6</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="B10" s="13">
+        <v>-500</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="11">
+        <v>-500</v>
+      </c>
+      <c r="J10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>6</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="B11" s="13">
+        <v>-250</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="11">
+        <v>-250</v>
+      </c>
+      <c r="J11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B12" s="13">
+        <v>-800</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>-800</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="11">
+        <v>-250</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="13"/>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12">
+        <v>-250</v>
+      </c>
+      <c r="I13" s="11">
+        <v>250</v>
+      </c>
       <c r="J13" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="13">
         <f>SUM(B5:B13)</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="10">
+        <v>11950</v>
+      </c>
+      <c r="C14" s="1">
         <f t="shared" ref="C14:I14" si="0">SUM(C5:C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="10">
+        <v>800</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="10">
+      <c r="G14" s="12">
         <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="H14" s="12">
+        <f t="shared" si="0"/>
+        <v>-250</v>
+      </c>
+      <c r="I14" s="11">
         <v>0</v>
       </c>
-      <c r="G14" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="8">
         <f>SUM(B14:D14)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="12">
+        <v>14750</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="9">
         <f>SUM(F14:I14)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
+        <v>14750</v>
+      </c>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2027,282 +2172,417 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8426FBE-EEC7-4097-8A0B-8FAEE5D9128F}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="4.54296875" style="10" customWidth="1"/>
-    <col min="3" max="7" width="8.7265625" style="10"/>
-    <col min="8" max="8" width="2.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="10"/>
+    <col min="1" max="2" width="4.5" customWidth="1"/>
+    <col min="8" max="8" width="2.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C3" s="10" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="10" t="s">
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C4" s="10" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="H4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="K4" s="12"/>
+      <c r="L4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="10" t="s">
+      <c r="M4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="13">
         <v>21000</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5">
         <v>12000</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5">
         <v>1500</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5">
         <v>108000</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" s="10">
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <v>4500</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5">
         <v>32000</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="12">
         <v>106000</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="10">
+      <c r="L5" s="12"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="10">
+      <c r="C6" s="13">
+        <v>10000</v>
+      </c>
+      <c r="D6">
+        <v>-10000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="10">
+      <c r="C7" s="13">
+        <v>-4500</v>
+      </c>
+      <c r="H7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <v>-4500</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>3</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="10">
+      <c r="C8" s="13">
+        <v>-16000</v>
+      </c>
+      <c r="F8">
+        <v>56000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>40000</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>4</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9">
+        <v>15500</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="1">
+        <v>15500</v>
+      </c>
+      <c r="N9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="10">
-        <v>5</v>
-      </c>
-      <c r="N10" s="10" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="H10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>4250</v>
+      </c>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="1">
+        <v>-4250</v>
+      </c>
+      <c r="N10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="10">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="C11" s="13">
+        <v>-3600</v>
+      </c>
+      <c r="H11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="1">
+        <v>-3600</v>
+      </c>
+      <c r="N11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B12" s="10" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="C12" s="13">
+        <v>-2050</v>
+      </c>
+      <c r="H12" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="1">
+        <v>-2050</v>
+      </c>
+      <c r="N12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="B13" s="10" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="N13" s="10" t="s">
+      <c r="C13" s="13">
+        <v>-1050</v>
+      </c>
+      <c r="H13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="1">
+        <v>-1050</v>
+      </c>
+      <c r="N13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="10">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="10">
+      <c r="C14" s="13">
+        <v>-4000</v>
+      </c>
+      <c r="H14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="12">
+        <v>-4000</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" t="s">
         <v>44</v>
       </c>
-      <c r="N15" s="10" t="s">
+      <c r="C15" s="13">
+        <v>-400</v>
+      </c>
+      <c r="H15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="1">
+        <v>-400</v>
+      </c>
+      <c r="N15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="N16" s="10" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C16" s="13"/>
+      <c r="H16" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12">
+        <v>4150</v>
+      </c>
+      <c r="M16" s="1">
+        <v>-4150</v>
+      </c>
+      <c r="N16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="10">
+      <c r="B17" s="14"/>
+      <c r="C17" s="13">
         <f>SUM(C5:C15)</f>
-        <v>21000</v>
-      </c>
-      <c r="D17" s="10">
+        <v>-600</v>
+      </c>
+      <c r="D17" s="14">
         <f>SUM(D5:D15)</f>
-        <v>12000</v>
-      </c>
-      <c r="E17" s="10">
+        <v>17500</v>
+      </c>
+      <c r="E17" s="14">
         <f>SUM(E5:E15)</f>
         <v>1500</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="14">
         <f>SUM(F5:F15)</f>
-        <v>108000</v>
-      </c>
-      <c r="G17" s="10">
+        <v>164000</v>
+      </c>
+      <c r="G17" s="14">
         <f>SUM(G5:G15)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="10">
+      <c r="H17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="14">
         <f>SUM(I5:I16)</f>
-        <v>4500</v>
-      </c>
-      <c r="J17" s="10">
+        <v>4250</v>
+      </c>
+      <c r="J17" s="14">
         <f t="shared" ref="J17:M17" si="0">SUM(J5:J16)</f>
-        <v>32000</v>
-      </c>
-      <c r="K17" s="10">
+        <v>72000</v>
+      </c>
+      <c r="K17" s="12">
         <f t="shared" si="0"/>
-        <v>106000</v>
-      </c>
-      <c r="L17" s="10">
+        <v>102000</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" si="0"/>
+        <v>4150</v>
+      </c>
+      <c r="M17" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M17" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C18" s="11">
+      <c r="N17" s="14"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15">
         <f>SUM(C17:G17)</f>
-        <v>142500</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="12">
+        <v>182400</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="16">
         <f>SUM(I17:M17)</f>
-        <v>142500</v>
-      </c>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
+        <v>182400</v>
+      </c>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2315,21 +2595,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D8A049-D767-4C2F-93F6-B57180128933}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.90625" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="13" max="13" width="14.26953125" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.5" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -2340,7 +2620,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -2372,7 +2652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="F4" t="s">
         <v>38</v>
       </c>
@@ -2389,7 +2669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2418,107 +2698,160 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>-28000</v>
+      </c>
+      <c r="L6">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="F7">
+        <v>19375</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <v>19375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="C8">
+        <v>6875</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>6875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="E9">
+        <v>5750</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="G10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>3125</v>
+      </c>
+      <c r="L10">
+        <v>-3125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="G11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B11">
-        <f>SUM(B5:B10)</f>
+      <c r="B12">
+        <f>SUM(B5:B11)</f>
         <v>31500</v>
       </c>
-      <c r="C11">
-        <f t="shared" ref="C11:K11" si="0">SUM(C5:C10)</f>
-        <v>43250</v>
-      </c>
-      <c r="D11">
+      <c r="C12">
+        <f t="shared" ref="C12:K12" si="0">SUM(C5:C11)</f>
+        <v>50125</v>
+      </c>
+      <c r="D12">
         <f t="shared" si="0"/>
         <v>52500</v>
       </c>
-      <c r="E11">
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>5750</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>19375</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>6875</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>35625</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>28000</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="0"/>
-        <v>32500</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="0"/>
-        <v>56000</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <f>SUM(L5:L10)</f>
-        <v>38750</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="L12">
+        <f>SUM(L5:L11)</f>
+        <v>88750</v>
+      </c>
+      <c r="M12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B12" s="8">
-        <f>SUM(B11:F11)</f>
-        <v>127250</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="9">
-        <f>SUM(H11:L11)</f>
-        <v>127250</v>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
+        <f>SUM(B12:F12)</f>
+        <v>159250</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="9">
+        <f>SUM(H12:L12)</f>
+        <v>159250</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="H13:L13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2528,7 +2861,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE1B0A9-3506-4701-A064-3A9B8A5C372A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2537,12 +2870,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397AC2CF-DBE2-4490-B2A9-DB3AB81F2978}">
   <dimension ref="B3:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
         <v>62</v>
       </c>
@@ -2553,7 +2886,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C4" t="s">
         <v>55</v>
       </c>
@@ -2565,7 +2898,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>56</v>
       </c>
@@ -2579,7 +2912,7 @@
         <v>12300</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -2590,7 +2923,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>57</v>
       </c>
@@ -2604,7 +2937,7 @@
         <v>-15000</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>58</v>
       </c>
@@ -2628,20 +2961,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC079501-4C0E-41F4-9E86-DF13FDEF1AF4}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2655,7 +2988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2684,7 +3017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
@@ -2708,7 +3041,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2725,7 +3058,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -2743,7 +3076,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2762,7 +3095,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -2781,7 +3114,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5</v>
       </c>
@@ -2800,7 +3133,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>6</v>
       </c>
@@ -2819,7 +3152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>6</v>
       </c>
@@ -2838,7 +3171,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>7</v>
       </c>
@@ -2856,7 +3189,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
       <c r="E13" t="s">
         <v>5</v>
@@ -2872,7 +3205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -2908,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -2941,18 +3274,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5860497F-FB9A-45B7-AE3A-A11B3AC82EF7}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="4.54296875" customWidth="1"/>
-    <col min="8" max="8" width="2.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="4.5" customWidth="1"/>
+    <col min="8" max="8" width="2.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -2966,7 +3299,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
@@ -3002,7 +3335,7 @@
       </c>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
@@ -3026,7 +3359,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3061,7 +3394,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3082,7 +3415,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3103,7 +3436,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>3</v>
       </c>
@@ -3127,7 +3460,7 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4</v>
       </c>
@@ -3147,7 +3480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5</v>
       </c>
@@ -3167,7 +3500,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>6</v>
       </c>
@@ -3189,7 +3522,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>44</v>
       </c>
@@ -3208,7 +3541,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>44</v>
       </c>
@@ -3227,7 +3560,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>7</v>
       </c>
@@ -3247,7 +3580,7 @@
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>8</v>
       </c>
@@ -3269,7 +3602,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C16" s="6"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3">
@@ -3282,7 +3615,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -3331,7 +3664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="8">

--- a/ACCY122/Tutorial/T01/T1.xlsx
+++ b/ACCY122/Tutorial/T01/T1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Tutorial/T01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Tutorial\T01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA3E82-95DC-F54B-952D-04300AF61269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071E22ED-1867-4ECB-ABF9-5A7168C51BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="520" windowWidth="33600" windowHeight="18760" activeTab="4" xr2:uid="{5791E237-50C4-4F3C-9FBA-44DBC18D103A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5791E237-50C4-4F3C-9FBA-44DBC18D103A}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="10" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="66">
   <si>
     <t>ASSETS</t>
   </si>
@@ -240,13 +240,39 @@
   </si>
   <si>
     <t>Net Profit</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">this question is testing whether you understand </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>adjustments (accrual accounting)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and where each item belongs</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +292,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -358,17 +392,17 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -420,8 +454,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1089208" y="653851"/>
-          <a:ext cx="5953179" cy="5855023"/>
+          <a:off x="1006279" y="660959"/>
+          <a:ext cx="5206817" cy="5928475"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -1492,7 +1526,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5266C6B8-DEA9-4608-AC99-9CB36941A1AB}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1501,21 +1535,21 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{143A62ED-56A0-4957-8F15-257DC59AE21C}">
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.5" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1526,7 +1560,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -1558,7 +1592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>38</v>
       </c>
@@ -1575,7 +1609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1604,7 +1638,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1621,7 +1655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1635,7 +1669,7 @@
         <v>6875</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1652,7 +1686,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
@@ -1669,7 +1703,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
@@ -1686,7 +1720,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1737,26 +1771,31 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B12" s="8">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="13">
         <f>SUM(B11:F11)</f>
         <v>159250</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
       <c r="G12" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="14">
         <f>SUM(H11:L11)</f>
         <v>159250</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1771,12 +1810,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F0F937E-4C12-4841-9156-FD60BA99C2BF}">
   <dimension ref="B3:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>62</v>
       </c>
@@ -1787,7 +1826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>55</v>
       </c>
@@ -1799,7 +1838,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>56</v>
       </c>
@@ -1809,7 +1848,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -1820,7 +1859,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>57</v>
       </c>
@@ -1834,7 +1873,7 @@
         <v>-15000</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>58</v>
       </c>
@@ -1858,20 +1897,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F189E0A-D987-4D06-A4FC-507AD72941BD}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1885,8 +1924,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
@@ -1901,21 +1940,21 @@
       <c r="F3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="9" t="s">
         <v>10</v>
       </c>
       <c r="J3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="13" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
@@ -1927,37 +1966,37 @@
       <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="11">
         <v>15000</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="10">
         <v>15000</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H5" s="10"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="11">
         <v>-2000</v>
       </c>
       <c r="D6">
@@ -1966,53 +2005,53 @@
       <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="11"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="11">
         <v>2000</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="11">
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="9">
         <v>2000</v>
       </c>
       <c r="J7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="11">
         <v>-1500</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="9">
         <v>-1500</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="11"/>
       <c r="C9">
         <v>800</v>
       </c>
@@ -2022,53 +2061,53 @@
       <c r="F9">
         <v>800</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="11">
         <v>-500</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="11">
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="9">
         <v>-500</v>
       </c>
       <c r="J10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <v>-250</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="11">
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="9">
         <v>-250</v>
       </c>
       <c r="J11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>7</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="11">
         <v>-800</v>
       </c>
       <c r="E12" t="s">
@@ -2077,41 +2116,41 @@
       <c r="F12">
         <v>-800</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="11">
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="9">
         <v>-250</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="13"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="11"/>
       <c r="E13" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10">
         <v>-250</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <v>250</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="11">
         <f>SUM(B5:B13)</f>
         <v>11950</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" ref="C14:I14" si="0">SUM(C5:C13)</f>
+        <f t="shared" ref="C14:H14" si="0">SUM(C5:C13)</f>
         <v>800</v>
       </c>
       <c r="D14" s="1">
@@ -2125,39 +2164,39 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="10">
         <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="10">
         <f t="shared" si="0"/>
         <v>-250</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <v>0</v>
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="13">
         <f>SUM(B14:D14)</f>
         <v>14750</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="14">
         <f>SUM(F14:I14)</f>
         <v>14750</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
       <c r="J15" s="1"/>
     </row>
   </sheetData>
@@ -2172,18 +2211,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8426FBE-EEC7-4097-8A0B-8FAEE5D9128F}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.5" customWidth="1"/>
-    <col min="8" max="8" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="8" max="8" width="2.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -2197,8 +2236,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C3" s="13" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
@@ -2222,18 +2261,18 @@
       <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="10" t="s">
         <v>33</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C4" s="13" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C4" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
@@ -2245,8 +2284,8 @@
       <c r="I4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12" t="s">
+      <c r="K4" s="10"/>
+      <c r="L4" s="10" t="s">
         <v>10</v>
       </c>
       <c r="M4" s="1" t="s">
@@ -2256,11 +2295,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="11">
         <v>21000</v>
       </c>
       <c r="D5">
@@ -2284,20 +2323,20 @@
       <c r="J5">
         <v>32000</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="10">
         <v>106000</v>
       </c>
-      <c r="L5" s="12"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="11">
         <v>10000</v>
       </c>
       <c r="D6">
@@ -2306,18 +2345,18 @@
       <c r="H6" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>-4500</v>
       </c>
       <c r="H7" t="s">
@@ -2326,18 +2365,18 @@
       <c r="I7">
         <v>-4500</v>
       </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>-16000</v>
       </c>
       <c r="F8">
@@ -2349,23 +2388,23 @@
       <c r="J8">
         <v>40000</v>
       </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C9" s="11"/>
       <c r="D9">
         <v>15500</v>
       </c>
       <c r="H9" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="1">
         <v>15500</v>
       </c>
@@ -2373,19 +2412,19 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
-      <c r="C10" s="13"/>
+      <c r="C10" s="11"/>
       <c r="H10" t="s">
         <v>5</v>
       </c>
       <c r="I10">
         <v>4250</v>
       </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
       <c r="M10" s="1">
         <v>-4250</v>
       </c>
@@ -2393,21 +2432,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="11">
         <v>-3600</v>
       </c>
       <c r="H11" t="s">
         <v>5</v>
       </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
       <c r="M11" s="1">
         <v>-3600</v>
       </c>
@@ -2415,18 +2454,18 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="11">
         <v>-2050</v>
       </c>
       <c r="H12" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
       <c r="M12" s="1">
         <v>-2050</v>
       </c>
@@ -2434,18 +2473,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="11">
         <v>-1050</v>
       </c>
       <c r="H13" t="s">
         <v>5</v>
       </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
       <c r="M13" s="1">
         <v>-1050</v>
       </c>
@@ -2453,40 +2492,40 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="11">
         <v>-4000</v>
       </c>
       <c r="H14" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="10">
         <v>-4000</v>
       </c>
-      <c r="L14" s="12"/>
+      <c r="L14" s="10"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="11">
         <v>-400</v>
       </c>
       <c r="H15" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
       <c r="M15" s="1">
         <v>-400</v>
       </c>
@@ -2494,13 +2533,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C16" s="13"/>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C16" s="11"/>
       <c r="H16" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12">
+      <c r="K16" s="10"/>
+      <c r="L16" s="10">
         <v>4150</v>
       </c>
       <c r="M16" s="1">
@@ -2510,47 +2549,47 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="13">
+      <c r="B17" s="12"/>
+      <c r="C17" s="11">
         <f>SUM(C5:C15)</f>
         <v>-600</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="12">
         <f>SUM(D5:D15)</f>
         <v>17500</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="12">
         <f>SUM(E5:E15)</f>
         <v>1500</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="12">
         <f>SUM(F5:F15)</f>
         <v>164000</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="12">
         <f>SUM(G5:G15)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="14">
+      <c r="H17" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="12">
         <f>SUM(I5:I16)</f>
         <v>4250</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="12">
         <f t="shared" ref="J17:M17" si="0">SUM(J5:J16)</f>
         <v>72000</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="10">
         <f t="shared" si="0"/>
         <v>102000</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="10">
         <f t="shared" si="0"/>
         <v>4150</v>
       </c>
@@ -2558,11 +2597,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N17" s="14"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
       <c r="C18" s="15">
         <f>SUM(C17:G17)</f>
         <v>182400</v>
@@ -2571,7 +2610,7 @@
       <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I18" s="16">
@@ -2582,7 +2621,7 @@
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
-      <c r="N18" s="14"/>
+      <c r="N18" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2595,21 +2634,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D8A049-D767-4C2F-93F6-B57180128933}">
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.5" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -2620,7 +2659,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>47</v>
       </c>
@@ -2652,7 +2691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="F4" t="s">
         <v>38</v>
       </c>
@@ -2669,7 +2708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -2698,7 +2737,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>0</v>
       </c>
@@ -2712,7 +2751,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2726,7 +2765,7 @@
         <v>19375</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
@@ -2740,7 +2779,7 @@
         <v>6875</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3</v>
       </c>
@@ -2754,7 +2793,7 @@
         <v>5750</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>4</v>
       </c>
@@ -2768,7 +2807,7 @@
         <v>-3125</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5</v>
       </c>
@@ -2776,7 +2815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -2827,26 +2866,31 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="8">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="13">
         <f>SUM(B12:F12)</f>
         <v>159250</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
       <c r="G13" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="14">
         <f>SUM(H12:L12)</f>
         <v>159250</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>65</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2861,7 +2905,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE1B0A9-3506-4701-A064-3A9B8A5C372A}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2870,12 +2914,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397AC2CF-DBE2-4490-B2A9-DB3AB81F2978}">
   <dimension ref="B3:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>62</v>
       </c>
@@ -2886,7 +2930,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>55</v>
       </c>
@@ -2898,7 +2942,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>56</v>
       </c>
@@ -2912,7 +2956,7 @@
         <v>12300</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>56</v>
       </c>
@@ -2923,7 +2967,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>57</v>
       </c>
@@ -2937,7 +2981,7 @@
         <v>-15000</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>58</v>
       </c>
@@ -2961,20 +3005,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC079501-4C0E-41F4-9E86-DF13FDEF1AF4}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2988,7 +3032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
@@ -3017,7 +3061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
@@ -3041,7 +3085,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3058,7 +3102,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
@@ -3076,7 +3120,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
@@ -3095,7 +3139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
@@ -3114,7 +3158,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
@@ -3133,7 +3177,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
@@ -3152,7 +3196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
@@ -3171,7 +3215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>7</v>
       </c>
@@ -3189,7 +3233,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
       <c r="E13" t="s">
         <v>5</v>
@@ -3205,7 +3249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -3241,26 +3285,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="13">
         <f>SUM(B14:D14)</f>
         <v>14750</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
       <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="14">
         <f>SUM(F14:I14)</f>
         <v>14750</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3274,18 +3318,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5860497F-FB9A-45B7-AE3A-A11B3AC82EF7}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.5" customWidth="1"/>
-    <col min="8" max="8" width="2.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="8" max="8" width="2.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -3299,7 +3343,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
@@ -3335,7 +3379,7 @@
       </c>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
@@ -3359,7 +3403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3394,7 +3438,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3415,7 +3459,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3436,7 +3480,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3</v>
       </c>
@@ -3460,7 +3504,7 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>4</v>
       </c>
@@ -3480,7 +3524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5</v>
       </c>
@@ -3500,7 +3544,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6</v>
       </c>
@@ -3522,7 +3566,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>44</v>
       </c>
@@ -3541,7 +3585,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>44</v>
       </c>
@@ -3560,7 +3604,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7</v>
       </c>
@@ -3580,7 +3624,7 @@
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>8</v>
       </c>
@@ -3602,7 +3646,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C16" s="6"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3">
@@ -3615,7 +3659,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -3664,28 +3708,28 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-      <c r="C18" s="8">
+      <c r="C18" s="13">
         <f>SUM(C17:G17)</f>
         <v>182400</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="14">
         <f>SUM(I17:M17)</f>
         <v>182400</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
